--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104664_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104664_W23.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8873</v>
+        <v>5.3398</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6935</v>
+        <v>4.6651</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1938</v>
+        <v>0.6746</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2402</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.632</v>
+        <v>0.4943</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3919</v>
+        <v>0.1695</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0945</v>
+        <v>1.9093</v>
       </c>
       <c r="K2" t="n">
-        <v>2.625</v>
+        <v>1.2993</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5306</v>
+        <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-1.2455</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.993</v>
+        <v>-0.805</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1387</v>
+        <v>-0.4405</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0743</v>
+        <v>1.9523</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3871</v>
+        <v>1.1703</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6871</v>
+        <v>0.782</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3461</v>
+        <v>2.7237</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8638</v>
+        <v>5.1167</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9997</v>
+        <v>3.9568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8641</v>
+        <v>1.1599</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6752</v>
+        <v>1.2307</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4993</v>
+        <v>1.6287</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1759</v>
+        <v>-0.398</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9454</v>
+        <v>2.0617</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3192</v>
+        <v>2.606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6263</v>
+        <v>-0.5443</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2702</v>
+        <v>-0.831</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8198</v>
+        <v>-0.9774</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>0.1463</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4569</v>
+        <v>1.3217</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4567</v>
+        <v>0.6965</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0002</v>
+        <v>0.6251</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7317</v>
+        <v>2.3367</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7317</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6984</v>
+        <v>2.9043</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5637</v>
+        <v>3.5937</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8654</v>
+        <v>-0.6894</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3524</v>
+        <v>1.7148</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1573</v>
+        <v>3.2685</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.805</v>
+        <v>-1.5537</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3799</v>
+        <v>3.1154</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3004</v>
+        <v>3.5853</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0795</v>
+        <v>-0.4698</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0275</v>
+        <v>-1.4006</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1431</v>
+        <v>-0.3168</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8844</v>
+        <v>-1.0838</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8223</v>
+        <v>0.6039</v>
       </c>
       <c r="T4" t="n">
-        <v>0.248</v>
+        <v>0.5757</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5743</v>
+        <v>0.0283</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1568</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.06419999999999999</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5408</v>
+        <v>2.7668</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3855</v>
+        <v>4.8849</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8447</v>
+        <v>-2.1181</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7158</v>
+        <v>2.347</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2698</v>
+        <v>3.1483</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.554</v>
+        <v>-0.8012</v>
       </c>
       <c r="J5" t="n">
-        <v>3.146</v>
+        <v>4.3505</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6019</v>
+        <v>3.2783</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4559</v>
+        <v>1.0722</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4302</v>
+        <v>-2.0034</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3321</v>
+        <v>-0.13</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0981</v>
+        <v>-1.8734</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7724</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6775</v>
+        <v>0.6059</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.095</v>
+        <v>0.2919</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>-1.1609</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4725</v>
+        <v>1.1664</v>
       </c>
       <c r="E6" t="n">
-        <v>2.06</v>
+        <v>1.6397</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5876</v>
+        <v>-0.4733</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2506</v>
+        <v>-1.2538</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1471</v>
+        <v>-0.1547</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1035</v>
+        <v>-1.0991</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2757</v>
+        <v>-0.295</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436</v>
+        <v>0.4202</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9749</v>
+        <v>-0.9588</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4962</v>
+        <v>1.1926</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2431</v>
+        <v>0.8452</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2531</v>
+        <v>0.3474</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.008</v>
+        <v>0.4796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5891</v>
+        <v>1.4026</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4189</v>
+        <v>-0.923</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1432</v>
+        <v>-1.2079</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1661</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3092</v>
+        <v>-1.2763</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1985</v>
+        <v>0.339</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0866</v>
+        <v>1.017</v>
       </c>
       <c r="L7" t="n">
-        <v>0.112</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0554</v>
+        <v>-1.5469</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2526</v>
+        <v>-0.9485</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1973</v>
+        <v>-0.5984</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8382</v>
+        <v>1.3217</v>
       </c>
       <c r="T7" t="n">
-        <v>1.364</v>
+        <v>1.0636</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4742</v>
+        <v>0.2581</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8803</v>
+        <v>0.2195</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6418</v>
+        <v>-0.7367</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7615</v>
+        <v>0.9563</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2216</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0605</v>
+        <v>-0.6093</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2821</v>
+        <v>1.3598</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3473</v>
+        <v>0.6063</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0217</v>
+        <v>0.5548</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6744</v>
+        <v>0.0515</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5689</v>
+        <v>0.1442</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-1.1642</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6077</v>
+        <v>1.3083</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7409</v>
+        <v>1.3113</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2945</v>
+        <v>0.7755</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4464</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8779</v>
+        <v>0.0902</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5825</v>
+        <v>1.7026</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7046</v>
+        <v>-1.6125</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3145</v>
+        <v>-0.3067</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2799</v>
+        <v>0.2814</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5944</v>
+        <v>-0.5881</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8495</v>
+        <v>0.8389</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7375</v>
+        <v>0.7272</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1639</v>
+        <v>-1.1457</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4704</v>
+        <v>1.6653</v>
       </c>
       <c r="T9" t="n">
-        <v>1.733</v>
+        <v>0.8637</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7373</v>
+        <v>0.8016</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3358</v>
+        <v>0.0585</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2252</v>
+        <v>-0.123</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1106</v>
+        <v>0.1815</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1492</v>
+        <v>0.1562</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6825</v>
+        <v>-0.1584</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5333</v>
+        <v>0.3145</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4013</v>
+        <v>0.1979</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0146</v>
+        <v>0.0862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6133</v>
+        <v>0.1117</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2521</v>
+        <v>-0.0417</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3321</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08</v>
+        <v>0.2028</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1601</v>
+        <v>0.8827</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3852</v>
+        <v>0.6595</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7748</v>
+        <v>0.2232</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4272</v>
+        <v>0.0027</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3164</v>
+        <v>-0.3908</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8892</v>
+        <v>0.3935</v>
       </c>
       <c r="G11" t="n">
-        <v>0.747</v>
+        <v>0.1342</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6177</v>
+        <v>0.6862</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3647</v>
+        <v>-0.552</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6309</v>
+        <v>0.3612</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5643</v>
+        <v>1.003</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0665</v>
+        <v>-0.6418</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1161</v>
+        <v>-0.227</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1821</v>
+        <v>-0.3168</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2982</v>
+        <v>0.0898</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6651</v>
+        <v>1.8488</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1603</v>
+        <v>0.8218</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5048</v>
+        <v>1.027</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5609</v>
+        <v>-1.8697</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8686</v>
+        <v>-0.6483</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6923</v>
+        <v>-1.2214</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6656</v>
+        <v>0.6597</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2627</v>
+        <v>1.2555</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5971</v>
+        <v>-0.5958</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4482</v>
+        <v>1.417</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7521</v>
+        <v>1.7302</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7825</v>
+        <v>-0.7573</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3853</v>
+        <v>0.3112</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0484</v>
+        <v>0.2111</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3369</v>
+        <v>0.1002</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.5767</v>
+        <v>16.2748</v>
       </c>
       <c r="E13" t="n">
-        <v>19.556</v>
+        <v>19.9466</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.979499999999999</v>
+        <v>-3.6719</v>
       </c>
       <c r="G13" t="n">
-        <v>4.901899999999999</v>
+        <v>4.8885</v>
       </c>
       <c r="H13" t="n">
-        <v>9.913100000000002</v>
+        <v>9.908999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.0115</v>
+        <v>-5.0204</v>
       </c>
       <c r="J13" t="n">
-        <v>15.1658</v>
+        <v>14.9022</v>
       </c>
       <c r="K13" t="n">
-        <v>16.4593</v>
+        <v>16.3075</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2935</v>
+        <v>-1.4051</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.2638</v>
+        <v>-10.0137</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.5461</v>
+        <v>-6.398700000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.7176</v>
+        <v>-3.6153</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R13" t="n">
-        <v>9.073300000000001</v>
+        <v>9.1053</v>
       </c>
       <c r="S13" t="n">
-        <v>12.5667</v>
+        <v>13.3092</v>
       </c>
       <c r="T13" t="n">
-        <v>7.546</v>
+        <v>8.2888</v>
       </c>
       <c r="U13" t="n">
-        <v>5.020300000000001</v>
+        <v>5.0206</v>
       </c>
       <c r="V13" t="n">
-        <v>1.510699999999999</v>
+        <v>1.491399999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>9.320100000000002</v>
+        <v>9.275499999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.809399999999999</v>
+        <v>-7.784</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5271</v>
+        <v>4.6959</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9686</v>
+        <v>7.041</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4415</v>
+        <v>-2.3451</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5749</v>
+        <v>3.5726</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8529</v>
+        <v>1.8443</v>
       </c>
       <c r="I14" t="n">
-        <v>1.722</v>
+        <v>1.7282</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7855</v>
+        <v>5.7509</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1835</v>
+        <v>4.1573</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2106</v>
+        <v>-2.1783</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3307</v>
+        <v>-2.313</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4599</v>
+        <v>-1.2833</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1875</v>
+        <v>-0.0678</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2724</v>
+        <v>-1.2155</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1958</v>
+        <v>1.2007</v>
       </c>
       <c r="E15" t="n">
-        <v>1.443</v>
+        <v>1.4256</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2472</v>
+        <v>-0.2249</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0336</v>
+        <v>0.0416</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2756</v>
+        <v>-0.273</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3092</v>
+        <v>0.3145</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0683</v>
+        <v>-0.0746</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1019</v>
+        <v>0.1162</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6109</v>
+        <v>-0.6132</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8347</v>
+        <v>-0.8364</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2238</v>
+        <v>0.2232</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8625</v>
+        <v>0.201</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3415</v>
+        <v>2.6158</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.479</v>
+        <v>-2.4148</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4908</v>
+        <v>0.5065</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="I16" t="n">
-        <v>0.208</v>
+        <v>0.2195</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7841</v>
+        <v>2.7717</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5975</v>
+        <v>2.5855</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2933</v>
+        <v>-2.2653</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.3148</v>
+        <v>-2.2986</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3088</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5989</v>
+        <v>-0.1072</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9076</v>
+        <v>-0.8812</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.4701</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6742</v>
+        <v>2.9292</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0325</v>
+        <v>-3.3993</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4525</v>
+        <v>1.4515</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7546</v>
+        <v>-0.7608</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2071</v>
+        <v>2.2123</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2972</v>
+        <v>4.2628</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5833</v>
+        <v>2.5576</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8446</v>
+        <v>-2.8112</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.3379</v>
+        <v>-3.3183</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0569</v>
+        <v>-1.0614</v>
       </c>
       <c r="T17" t="n">
-        <v>0.738</v>
+        <v>0.0322</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6811</v>
+        <v>-1.0936</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7611</v>
+        <v>-1.5831</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6515</v>
+        <v>-0.1736</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1095</v>
+        <v>-1.4095</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1869</v>
+        <v>-1.5459</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4055</v>
+        <v>0.7319</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2186</v>
+        <v>-2.2778</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3299</v>
+        <v>-0.0571</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5857</v>
+        <v>1.7237</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2558</v>
+        <v>-1.7808</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.857</v>
+        <v>-1.4888</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8198</v>
+        <v>-0.9918</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0372</v>
+        <v>-0.497</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7744</v>
+        <v>-1.4924</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3217</v>
+        <v>-1.2059</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4528</v>
+        <v>-0.2865</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. KLJAJIC</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8197</v>
+        <v>-1.6103</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0272</v>
+        <v>-1.4389</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8469</v>
+        <v>-0.1713</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4434</v>
+        <v>-1.1797</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5281</v>
+        <v>-1.4018</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0848</v>
+        <v>0.2221</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4033</v>
+        <v>-0.3515</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.111</v>
+        <v>-0.5968</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5143</v>
+        <v>0.2453</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8467</v>
+        <v>-0.8282</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4171</v>
+        <v>-0.805</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5705</v>
+        <v>-0.0232</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4425</v>
+        <v>-1.6386</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4386</v>
+        <v>-1.0875</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.881</v>
+        <v>-0.5512</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7071</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>J. KLJAJIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1094</v>
+        <v>-1.692</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.262</v>
+        <v>-0.1175</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8474</v>
+        <v>-1.5745</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.551</v>
+        <v>-0.4517</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7228</v>
+        <v>-1.5252</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2737</v>
+        <v>1.0735</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.033</v>
+        <v>0.3809</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7317</v>
+        <v>-0.1174</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7647</v>
+        <v>0.4983</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5179</v>
+        <v>-0.8326</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0089</v>
+        <v>-1.4078</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.509</v>
+        <v>0.5752</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0122</v>
+        <v>-0.3101</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3217</v>
+        <v>0.3227</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6905</v>
+        <v>-0.6328</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5463</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.279</v>
+        <v>-2.7414</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4097</v>
+        <v>-2.0766</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8693</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6375</v>
+        <v>-2.6426</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1875</v>
+        <v>-1.1917</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4501</v>
+        <v>-1.4509</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3481</v>
+        <v>-1.3679</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2894</v>
+        <v>-1.2747</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0951</v>
+        <v>-0.5541</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2604</v>
+        <v>-0.073</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.859</v>
+        <v>-4.2796</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4329</v>
+        <v>0.6289</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.2919</v>
+        <v>-4.9085</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1085</v>
+        <v>0.1014</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4877</v>
+        <v>-2.4872</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5962</v>
+        <v>2.5886</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7728</v>
+        <v>1.7349</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.6625</v>
       </c>
       <c r="L22" t="n">
-        <v>2.4175</v>
+        <v>2.3974</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6643</v>
+        <v>-1.6335</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8429</v>
+        <v>-1.8248</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3699</v>
+        <v>-1.7955</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.113</v>
+        <v>-0.8784</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.257</v>
+        <v>-0.9171</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.9755</v>
+        <v>-8.5091</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.5847</v>
+        <v>-7.162</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3907</v>
+        <v>-1.3471</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.7434</v>
+        <v>-4.7421</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.1326</v>
+        <v>-5.1324</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3892</v>
+        <v>0.3903</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9997</v>
+        <v>-3.0363</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.5811</v>
+        <v>-2.6037</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4186</v>
+        <v>-0.4326</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7437</v>
+        <v>-1.7057</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.5515</v>
+        <v>-2.5287</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8078</v>
+        <v>0.8229</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.5496</v>
+        <v>-2.0857</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1825</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3671</v>
+        <v>-1.3746</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.5767</v>
+        <v>-14.788</v>
       </c>
       <c r="E24" t="n">
-        <v>3.9795</v>
+        <v>3.671899999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-19.5559</v>
+        <v>-18.4598</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.9019</v>
+        <v>-4.8884</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.9131</v>
+        <v>-9.908899999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>5.011300000000001</v>
+        <v>5.0203</v>
       </c>
       <c r="J24" t="n">
-        <v>10.2639</v>
+        <v>10.0138</v>
       </c>
       <c r="K24" t="n">
-        <v>6.5461</v>
+        <v>6.398400000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>3.7177</v>
+        <v>3.6152</v>
       </c>
       <c r="M24" t="n">
-        <v>-15.1656</v>
+        <v>-14.9021</v>
       </c>
       <c r="N24" t="n">
-        <v>-16.4594</v>
+        <v>-16.3074</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2938</v>
+        <v>1.4051</v>
       </c>
       <c r="P24" t="n">
-        <v>3.402500000000001</v>
+        <v>3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R24" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S24" t="n">
-        <v>-12.5664</v>
+        <v>-11.8227</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.020300000000001</v>
+        <v>-5.0206</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.546099999999999</v>
+        <v>-6.8023</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5107</v>
+        <v>-1.491400000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>7.8095</v>
+        <v>7.7841</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.32</v>
+        <v>-9.2753</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104664_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104664_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.784</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104664_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.2753</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
